--- a/artfynd/S 212-2024 artfynd.xlsx
+++ b/artfynd/S 212-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135018500</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135018493</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118323617</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1137,6 +1157,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62805113</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98669422</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1374,6 +1404,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/224873</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1485,6 +1520,11 @@
           <t>Åtgärdsprogram liten havstulpanlav</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/225653</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1601,6 +1641,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/226408</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1712,6 +1757,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/226878</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1821,6 +1871,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98669512</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1926,6 +1981,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103712674</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2031,6 +2091,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98669502</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2136,6 +2201,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98669418</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2237,6 +2307,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103712927</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2356,6 +2431,11 @@
           <t>Åtgärdsprogram liten havstulpanlav</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/452632</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2476,6 +2556,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/582376</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2600,6 +2685,11 @@
           <t>Åtgärdsprogram liten havstulpanlav</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/583500</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2724,6 +2814,11 @@
           <t>Åtgärdsprogram liten havstulpanlav</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/583501</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2848,6 +2943,11 @@
           <t>Åtgärdsprogram liten havstulpanlav</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/583502</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2972,6 +3072,11 @@
           <t>Åtgärdsprogram liten havstulpanlav</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/583505</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3091,6 +3196,11 @@
           <t>Åtgärdsprogram liten havstulpanlav</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/583522</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3210,6 +3320,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67536237</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3315,6 +3430,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98669083</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3429,6 +3549,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120392728</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3534,6 +3659,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98669431</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3653,6 +3783,11 @@
           <t>Åtgärdsprogram liten havstulpanlav</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1867007</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3772,6 +3907,11 @@
           <t>Åtgärdsprogram liten havstulpanlav</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6547489</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3896,6 +4036,11 @@
           <t>Åtgärdsprogram liten havstulpanlav</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6539713</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4006,6 +4151,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98669786</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4113,6 +4263,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120432674</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4215,6 +4370,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120432645</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4333,6 +4493,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61259080</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4444,8 +4609,48 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68440885</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 212-2024 artfynd.xlsx
+++ b/artfynd/S 212-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135018500</v>
       </c>
       <c r="B2" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>135018493</v>
       </c>
       <c r="B3" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
